--- a/artfynd/A 66992-2021 artfynd.xlsx
+++ b/artfynd/A 66992-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134020704</v>
       </c>
       <c r="B2" t="n">
-        <v>56882</v>
+        <v>56889</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 66992-2021 artfynd.xlsx
+++ b/artfynd/A 66992-2021 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>134020704</v>
       </c>
       <c r="B2" t="n">
-        <v>56889</v>
+        <v>56899</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 66992-2021 artfynd.xlsx
+++ b/artfynd/A 66992-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134020704</v>
+        <v>17347408</v>
       </c>
       <c r="B2" t="n">
-        <v>56899</v>
+        <v>56879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -708,32 +708,28 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>hane</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vilande</t>
+        </is>
+      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Rafshagvägen västra, Sm</t>
+          <t>Björnö grustag, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>581555</v>
+        <v>581761</v>
       </c>
       <c r="R2" t="n">
-        <v>6291605</v>
+        <v>6291615</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -757,12 +753,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2015-04-18</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2015-04-18</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -771,26 +767,1273 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134020704</v>
+      </c>
+      <c r="B3" t="n">
+        <v>56899</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Rafshagvägen västra, Sm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>581555</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6291605</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Lucia Caroli</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr">
+      <c r="AY3" t="inlineStr">
         <is>
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>134020705</v>
+      </c>
+      <c r="B4" t="n">
+        <v>56899</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Rafshagvägen västra, Sm</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>581655</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6291643</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Lucia Caroli</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>134020706</v>
+      </c>
+      <c r="B5" t="n">
+        <v>56899</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>hane</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Rafshagvägen västra, Sm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>581667</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6291652</v>
+      </c>
+      <c r="S5" t="n">
+        <v>5</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Lucia Caroli</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>134020707</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56899</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Rafshagvägen västra, Sm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>581686</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6291653</v>
+      </c>
+      <c r="S6" t="n">
+        <v>5</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Lucia Caroli</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>134020709</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56899</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Rafshagvägen västra, Sm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>581643</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6291652</v>
+      </c>
+      <c r="S7" t="n">
+        <v>5</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Lucia Caroli</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>134020710</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56899</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Rafshagvägen västra, Sm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>581659</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6291656</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lucia Caroli</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>134020711</v>
+      </c>
+      <c r="B9" t="n">
+        <v>56899</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>100070</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Sandödla</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lacerta agilis</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Rafshagvägen västra, Sm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>581689</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6291658</v>
+      </c>
+      <c r="S9" t="n">
+        <v>5</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Lucia Caroli</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>16037478</v>
+      </c>
+      <c r="B10" t="n">
+        <v>45044</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>102018</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bredbrämad bastardsvärmare</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Zygaena lonicerae</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Scheven, 1777)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Björnö grustag, Sm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>581761</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6291615</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2014-06-29</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2014-06-29</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>118333899</v>
+      </c>
+      <c r="B11" t="n">
+        <v>102419</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>221317</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gullklöver</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Trifolium aureum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Pollich</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Björnö grustag, Sm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>581761</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6291615</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-07-09</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>96378421</v>
+      </c>
+      <c r="B12" t="n">
+        <v>97986</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>221946</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Mattlummer</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lycopodium clavatum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Björnö grustag, Sm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>581761</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6291615</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-09-30</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Ulla Kruys, Ivan Kruys</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>16037869</v>
+      </c>
+      <c r="B13" t="n">
+        <v>106347</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>224199</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Småsnärjmåra</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Galium spurium subsp. vaillantii</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(DC.) Gaudin</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Björnö grustag, Sm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>581761</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6291615</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Åby</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2014-06-29</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2014-06-29</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Ulla Kruys</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 66992-2021 artfynd.xlsx
+++ b/artfynd/A 66992-2021 artfynd.xlsx
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+          <t>Lucia Caroli, Tyra Westelius, Tobias Uller</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+          <t>Lucia Caroli, Tyra Westelius, Tobias Uller</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
+          <t>Lucia Caroli, Tyra Westelius, Tobias Uller</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 66992-2021 artfynd.xlsx
+++ b/artfynd/A 66992-2021 artfynd.xlsx
@@ -1245,7 +1245,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tyra Westelius, Tobias Uller</t>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1359,7 +1359,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tyra Westelius, Tobias Uller</t>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Lucia Caroli, Tyra Westelius, Tobias Uller</t>
+          <t>Lucia Caroli, Tobias Uller, Tyra Westelius</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 66992-2021 artfynd.xlsx
+++ b/artfynd/A 66992-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AZ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17347408</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -901,6 +911,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020704</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,6 +1030,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020705</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1134,6 +1154,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020706</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1253,6 +1278,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020707</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1367,6 +1397,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020709</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1481,6 +1516,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020710</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,6 +1640,11 @@
           <t>Identifiering av hot och effektiva bevarandestrategier av sandödla via genomisk analys - FORMAS</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134020711</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1714,6 +1759,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16037478</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1820,6 +1870,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118333899</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1930,6 +1985,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96378421</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2034,8 +2094,27 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/16037869</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>